--- a/Result/profitability/8150.xlsx
+++ b/Result/profitability/8150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM65"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.275</v>
+        <v>0.3825</v>
       </c>
       <c r="N2" t="n">
-        <v>11.22875</v>
+        <v>11.73625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-3.95</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.27</v>
+        <v>-0.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>8.46625</v>
+        <v>9.52</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-3.43</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.73875</v>
+        <v>-0.6100000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>2.048749999999999</v>
+        <v>3.122499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.7450000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.741250000000001</v>
+        <v>-0.3212500000000005</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,25 +1137,25 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7787500000000001</v>
+        <v>-0.6825000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.890000000000001</v>
+        <v>-2.19125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.86</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.60875</v>
+        <v>-0.5375000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.50125</v>
+        <v>-3.050000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8683,6 +8683,133 @@
       </c>
       <c r="AM65" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7383</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6057</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1326</v>
+      </c>
+      <c r="F66" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G66" t="n">
+        <v>948</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>12.84%</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>79</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1027</v>
+      </c>
+      <c r="K66" t="n">
+        <v>892</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="N66" t="n">
+        <v>12.2325</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.7638888888888891</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>4.180000000000001</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.3033381712626997</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-2.693333333333333</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.721212121212122</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
